--- a/data/high.xlsx
+++ b/data/high.xlsx
@@ -21,220 +21,220 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="75">
   <x:si>
+    <x:t>031-313-6100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7014-4342</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 금오로 640</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-310-9000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-365-8365</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 은행고길 85</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 승지로 107</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-363-5100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-362-8400</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 금오로 103</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 매화로 35</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02-2610-4600</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기스마트고등학교(복합특수)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(복특+시간+순회+일반)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 상직길 25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-460-8900</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 역전로 463</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-489-8114</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-500-5201</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-488-5333</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-363-1525</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-8708-2117</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-8042-7150</x:t>
+  </x:si>
+  <x:si>
     <x:t>경기도 시흥시 포도원로 50</x:t>
   </x:si>
   <x:si>
+    <x:t>복특1/시간제2/순회1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-8084-8102</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-430-8226</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-317-2744</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-496-2969</x:t>
+  </x:si>
+  <x:si>
+    <x:t>군자디지털과학고등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>장곡고등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>함현고등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>목감고등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>은행고등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3/ 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>신천고등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>군서고등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소래고등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>서해고등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>정왕고등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥고등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배곧고등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22/ 4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>한국조리과학고등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥매화고등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(특수/순회/일반)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥능곡고등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기자동차과학고등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>군서미래국제학교(고)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 목감둘레로 150</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 군자로487번길 54</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 군서마을로 100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 봉우재로 37번길 5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 배곧 4로 94-10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 정왕신길로 13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 정왕천로 404</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 장곡로 70번길 8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 정왕대로 118번길 13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 수인로 3287번길 26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-</x:t>
+  </x:si>
+  <x:si>
+    <x:t>비고</x:t>
+  </x:si>
+  <x:si>
+    <x:t>유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공립</x:t>
+  </x:si>
+  <x:si>
+    <x:t>사립</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>위도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4/ 11/ 5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>특수/순회학급 배치 학생 수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>일반학급 배치 학생 수</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 주소</x:t>
+  </x:si>
+  <x:si>
     <x:t>보조인력 배치 유/무</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve"> 특수/순회학급수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02-2610-4600</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-500-5201</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기스마트고등학교(복합특수)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-317-2744</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7014-4342</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(복특+시간+순회+일반)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-488-5333</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-313-6100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 상직길 25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 매화로 35</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 금오로 103</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 승지로 107</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 역전로 463</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 금오로 640</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-362-8400</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-460-8900</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-8042-7150</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-8708-2117</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-363-5100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 봉우재로 37번길 5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-430-8226</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-489-8114</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-363-1525</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 은행고길 85</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-310-9000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-496-2969</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-8084-8102</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-365-8365</x:t>
-  </x:si>
-  <x:si>
-    <x:t>복특1/시간제2/순회1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4/ 12/ 4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기자동차과학고등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>한국조리과학고등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(특수/순회/일반)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥매화고등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>군서미래국제학교(고)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥능곡고등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>군자디지털과학고등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 정왕천로 404</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 정왕신길로 13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 배곧 4로 94-10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 군서마을로 100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 장곡로 70번길 8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 군자로487번길 54</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 목감둘레로 150</x:t>
-  </x:si>
-  <x:si>
-    <x:t>목감고등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>함현고등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>비고</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>위도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>사립</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공립</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-</x:t>
-  </x:si>
-  <x:si>
-    <x:t>유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 수인로 3287번길 26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 정왕대로 118번길 13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>은행고등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배곧고등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정왕고등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>군서고등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>소래고등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>신천고등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22/ 4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥고등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>서해고등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3/ 1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>장곡고등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>특수/순회학급 배치 학생 수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>일반학급 배치 학생 수</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 주소</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve"> 학교설립별</x:t>
@@ -774,60 +774,60 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="C1" t="s">
-        <x:v>71</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D1" t="s">
         <x:v>73</x:v>
       </x:c>
       <x:c r="E1" t="s">
-        <x:v>2</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="F1" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="G1" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="H1" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="H1" t="s">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="I1" t="s">
-        <x:v>49</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="J1" t="s">
-        <x:v>51</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="K1" t="s">
-        <x:v>50</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:11" ht="39.54999999999999715783">
       <x:c r="A2" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E2" s="2" t="s">
-        <x:v>31</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F2" s="2" t="s">
-        <x:v>32</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="G2" s="3">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H2" s="4" t="s">
-        <x:v>55</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="I2" s="5" t="s">
-        <x:v>8</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="J2" s="6">
         <x:v>37.343459867978297</x:v>
@@ -838,16 +838,16 @@
     </x:row>
     <x:row r="3" spans="1:11" ht="39.54999999999999715783">
       <x:c r="A3" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E3" s="7">
         <x:v>0</x:v>
@@ -859,7 +859,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H3" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="I3" s="5"/>
       <x:c r="J3" s="6">
@@ -871,16 +871,16 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="26.35000000000000142109">
       <x:c r="A4" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E4" s="9">
         <x:v>2</x:v>
@@ -892,7 +892,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="H4" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="I4" s="5"/>
       <x:c r="J4" s="6">
@@ -904,16 +904,16 @@
     </x:row>
     <x:row r="5" spans="1:11" ht="26.35000000000000142109">
       <x:c r="A5" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E5" s="7">
         <x:v>0</x:v>
@@ -925,7 +925,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H5" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="I5" s="5"/>
       <x:c r="J5" s="6">
@@ -937,31 +937,31 @@
     </x:row>
     <x:row r="6" spans="1:11" ht="39.54999999999999715783">
       <x:c r="A6" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E6" s="10" t="s">
-        <x:v>67</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F6" s="11" t="s">
-        <x:v>64</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="G6" s="3">
         <x:v>2</x:v>
       </x:c>
       <x:c r="H6" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="I6" s="5" t="s">
-        <x:v>35</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="J6" s="6">
         <x:v>37.349803420991499</x:v>
@@ -972,16 +972,16 @@
     </x:row>
     <x:row r="7" spans="1:11" ht="26.35000000000000142109">
       <x:c r="A7" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E7" s="9">
         <x:v>2</x:v>
@@ -993,7 +993,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="H7" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="I7" s="5"/>
       <x:c r="J7" s="6">
@@ -1005,16 +1005,16 @@
     </x:row>
     <x:row r="8" spans="1:11" ht="26.35000000000000142109">
       <x:c r="A8" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="C8" s="1" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="C8" s="1" t="s">
-        <x:v>42</x:v>
-      </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E8" s="9">
         <x:v>2</x:v>
@@ -1026,7 +1026,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="H8" s="4" t="s">
-        <x:v>55</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="I8" s="5"/>
       <x:c r="J8" s="6">
@@ -1038,13 +1038,13 @@
     </x:row>
     <x:row r="9" spans="1:11" ht="26.35000000000000142109">
       <x:c r="A9" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
         <x:v>28</x:v>
@@ -1059,7 +1059,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="H9" s="4" t="s">
-        <x:v>55</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="I9" s="5"/>
       <x:c r="J9" s="6">
@@ -1071,16 +1071,16 @@
     </x:row>
     <x:row r="10" spans="1:11" ht="26.35000000000000142109">
       <x:c r="A10" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E10" s="9">
         <x:v>1</x:v>
@@ -1092,7 +1092,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="H10" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="I10" s="5"/>
       <x:c r="J10" s="6">
@@ -1104,16 +1104,16 @@
     </x:row>
     <x:row r="11" spans="1:11" ht="26.35000000000000142109">
       <x:c r="A11" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E11" s="9">
         <x:v>2</x:v>
@@ -1125,7 +1125,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="H11" s="4" t="s">
-        <x:v>55</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="I11" s="5"/>
       <x:c r="J11" s="6">
@@ -1137,16 +1137,16 @@
     </x:row>
     <x:row r="12" spans="1:11" ht="26.35000000000000142109">
       <x:c r="A12" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E12" s="9">
         <x:v>2</x:v>
@@ -1158,7 +1158,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="H12" s="4" t="s">
-        <x:v>55</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="I12" s="5"/>
       <x:c r="J12" s="6">
@@ -1170,16 +1170,16 @@
     </x:row>
     <x:row r="13" spans="1:11" ht="26.35000000000000142109">
       <x:c r="A13" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E13" s="9">
         <x:v>1</x:v>
@@ -1191,7 +1191,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H13" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="I13" s="5"/>
       <x:c r="J13" s="6">
@@ -1203,16 +1203,16 @@
     </x:row>
     <x:row r="14" spans="1:11" ht="26.35000000000000142109">
       <x:c r="A14" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>0</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E14" s="9">
         <x:v>3</x:v>
@@ -1224,7 +1224,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H14" s="4" t="s">
-        <x:v>55</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="I14" s="5"/>
       <x:c r="J14" s="6">
@@ -1236,16 +1236,16 @@
     </x:row>
     <x:row r="15" spans="1:11" ht="26.35000000000000142109">
       <x:c r="A15" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E15" s="9">
         <x:v>3</x:v>
@@ -1257,7 +1257,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="H15" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="I15" s="5"/>
       <x:c r="J15" s="6">
@@ -1269,16 +1269,16 @@
     </x:row>
     <x:row r="16" spans="1:11" ht="26.35000000000000142109">
       <x:c r="A16" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E16" s="9">
         <x:v>2</x:v>
@@ -1290,7 +1290,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="H16" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="I16" s="5"/>
       <x:c r="J16" s="6">
@@ -1302,16 +1302,16 @@
     </x:row>
     <x:row r="17" spans="1:11" ht="26.35000000000000142109">
       <x:c r="A17" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
         <x:v>57</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E17" s="7">
         <x:v>0</x:v>
@@ -1323,7 +1323,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="H17" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="I17" s="5"/>
       <x:c r="J17" s="6">
@@ -1335,16 +1335,16 @@
     </x:row>
     <x:row r="18" spans="1:11" ht="26.35000000000000142109">
       <x:c r="A18" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E18" s="7">
         <x:v>0</x:v>
@@ -1356,7 +1356,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H18" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="I18" s="5"/>
       <x:c r="J18" s="6">
@@ -1368,16 +1368,16 @@
     </x:row>
     <x:row r="19" spans="1:11" ht="26.35000000000000142109">
       <x:c r="A19" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E19" s="9">
         <x:v>2</x:v>
@@ -1389,7 +1389,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H19" s="4" t="s">
-        <x:v>55</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="I19" s="5"/>
       <x:c r="J19" s="6">
@@ -1400,7 +1400,7 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51152777671813964844" footer="0.51152777671813964844"/>
+  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51138889789581298828" footer="0.51138889789581298828"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="0" verticalDpi="0" copies="1"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="1" alignWithMargins="1"/>
 </x:worksheet>

--- a/data/high.xlsx
+++ b/data/high.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="28545" windowHeight="11325" tabRatio="500"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="28545" windowHeight="12180" tabRatio="500"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="high" sheetId="1" r:id="rId4"/>
@@ -21,229 +21,229 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="75">
   <x:si>
+    <x:t xml:space="preserve"> 학교설립별</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 학교명</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 연락처</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 주소</x:t>
+  </x:si>
+  <x:si>
+    <x:t>비고</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 정왕천로 404</x:t>
+  </x:si>
+  <x:si>
+    <x:t>복특1/시간제2/순회1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(복특+시간+순회+일반)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-363-5100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-362-8400</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-317-2744</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-430-8226</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-496-2969</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 상직길 25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-489-8114</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 포도원로 50</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-8084-8102</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기스마트고등학교(복합특수)</x:t>
+  </x:si>
+  <x:si>
     <x:t>031-313-6100</x:t>
   </x:si>
   <x:si>
+    <x:t>031-488-5333</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-500-5201</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-363-1525</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 금오로 103</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 매화로 35</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02-2610-4600</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 금오로 640</x:t>
+  </x:si>
+  <x:si>
     <x:t>070-7014-4342</x:t>
   </x:si>
   <x:si>
-    <x:t>경기도 시흥시 금오로 640</x:t>
-  </x:si>
-  <x:si>
     <x:t>031-310-9000</x:t>
   </x:si>
   <x:si>
+    <x:t>031-460-8900</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 역전로 463</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 은행고길 85</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-8708-2117</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-8042-7150</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 승지로 107</x:t>
+  </x:si>
+  <x:si>
     <x:t>031-365-8365</x:t>
   </x:si>
   <x:si>
-    <x:t>경기도 시흥시 은행고길 85</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 승지로 107</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-363-5100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-362-8400</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 금오로 103</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 매화로 35</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02-2610-4600</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기스마트고등학교(복합특수)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(복특+시간+순회+일반)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 상직길 25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-460-8900</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 역전로 463</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-489-8114</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-500-5201</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-488-5333</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-363-1525</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-8708-2117</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-8042-7150</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 포도원로 50</x:t>
-  </x:si>
-  <x:si>
-    <x:t>복특1/시간제2/순회1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-8084-8102</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-430-8226</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-317-2744</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-496-2969</x:t>
+    <x:t>경기도 시흥시 장곡로 70번길 8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 정왕신길로 13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 군서마을로 100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4/ 11/ 4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기자동차과학고등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>군서미래국제학교(고)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배곧고등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22/ 4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>장곡고등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3/ 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>함현고등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>목감고등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>은행고등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>신천고등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>서해고등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소래고등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>정왕고등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥고등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>군서고등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 정왕대로 118번길 13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 수인로 3287번길 26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 배곧 4로 94-10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 봉우재로 37번길 5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 목감둘레로 150</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 군자로487번길 54</x:t>
+  </x:si>
+  <x:si>
+    <x:t>위도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-</x:t>
+  </x:si>
+  <x:si>
+    <x:t>유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>사립</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공립</x:t>
   </x:si>
   <x:si>
     <x:t>군자디지털과학고등학교</x:t>
   </x:si>
   <x:si>
-    <x:t>장곡고등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>함현고등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>목감고등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>은행고등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3/ 1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>신천고등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>군서고등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>소래고등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>서해고등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정왕고등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥고등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배곧고등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22/ 4</x:t>
+    <x:t>시흥매화고등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(특수/순회/일반)</x:t>
   </x:si>
   <x:si>
     <x:t>한국조리과학고등학교</x:t>
   </x:si>
   <x:si>
-    <x:t>시흥매화고등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(특수/순회/일반)</x:t>
-  </x:si>
-  <x:si>
     <x:t>시흥능곡고등학교</x:t>
   </x:si>
   <x:si>
-    <x:t>경기자동차과학고등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>군서미래국제학교(고)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 목감둘레로 150</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 군자로487번길 54</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 군서마을로 100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 봉우재로 37번길 5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 배곧 4로 94-10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 정왕신길로 13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 정왕천로 404</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 장곡로 70번길 8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 정왕대로 118번길 13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 수인로 3287번길 26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-</x:t>
-  </x:si>
-  <x:si>
-    <x:t>비고</x:t>
-  </x:si>
-  <x:si>
-    <x:t>유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공립</x:t>
-  </x:si>
-  <x:si>
-    <x:t>사립</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>위도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4/ 11/ 5</x:t>
+    <x:t xml:space="preserve"> 특수/순회학급수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>보조인력 배치 유/무</x:t>
   </x:si>
   <x:si>
     <x:t>특수/순회학급 배치 학생 수</x:t>
   </x:si>
   <x:si>
     <x:t>일반학급 배치 학생 수</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 주소</x:t>
-  </x:si>
-  <x:si>
-    <x:t>보조인력 배치 유/무</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 특수/순회학급수</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 학교설립별</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 연락처</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 학교명</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -307,11 +307,26 @@
         </x:font>
       </mc:Fallback>
     </mc:AlternateContent>
-    <x:font>
-      <x:name val="돋움"/>
-      <x:sz val="11"/>
-      <x:color rgb="ff000000"/>
-    </x:font>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:font hs:extension="1">
+          <x:name val="돋움"/>
+          <x:sz val="11"/>
+          <x:color rgb="ff000000"/>
+          <hs:size val="100"/>
+          <hs:ratio val="100"/>
+          <hs:spacing val="0"/>
+          <hs:offset val="0"/>
+        </x:font>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:font>
+          <x:name val="돋움"/>
+          <x:sz val="11"/>
+          <x:color rgb="ff000000"/>
+        </x:font>
+      </mc:Fallback>
+    </mc:AlternateContent>
   </x:fonts>
   <x:fills count="2">
     <x:fill>
@@ -768,66 +783,66 @@
   <x:sheetData>
     <x:row r="1" spans="1:11">
       <x:c r="A1" t="s">
-        <x:v>74</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B1" t="s">
-        <x:v>72</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C1" t="s">
-        <x:v>69</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D1" t="s">
-        <x:v>73</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E1" t="s">
         <x:v>71</x:v>
       </x:c>
       <x:c r="F1" t="s">
-        <x:v>67</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="G1" t="s">
-        <x:v>68</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="H1" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="I1" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="J1" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="J1" t="s">
-        <x:v>65</x:v>
-      </x:c>
       <x:c r="K1" t="s">
-        <x:v>64</x:v>
+        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:11" ht="39.54999999999999715783">
       <x:c r="A2" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E2" s="2" t="s">
-        <x:v>24</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F2" s="2" t="s">
-        <x:v>66</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G2" s="3">
         <x:v>1</x:v>
       </x:c>
       <x:c r="H2" s="4" t="s">
-        <x:v>61</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="I2" s="5" t="s">
-        <x:v>13</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="J2" s="6">
         <x:v>37.343459867978297</x:v>
@@ -838,16 +853,16 @@
     </x:row>
     <x:row r="3" spans="1:11" ht="39.54999999999999715783">
       <x:c r="A3" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E3" s="7">
         <x:v>0</x:v>
@@ -859,7 +874,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H3" s="4" t="s">
-        <x:v>59</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="I3" s="5"/>
       <x:c r="J3" s="6">
@@ -871,16 +886,16 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="26.35000000000000142109">
       <x:c r="A4" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E4" s="9">
         <x:v>2</x:v>
@@ -892,7 +907,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="H4" s="4" t="s">
-        <x:v>59</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="I4" s="5"/>
       <x:c r="J4" s="6">
@@ -904,16 +919,16 @@
     </x:row>
     <x:row r="5" spans="1:11" ht="26.35000000000000142109">
       <x:c r="A5" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E5" s="7">
         <x:v>0</x:v>
@@ -925,7 +940,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H5" s="4" t="s">
-        <x:v>59</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="I5" s="5"/>
       <x:c r="J5" s="6">
@@ -937,19 +952,19 @@
     </x:row>
     <x:row r="6" spans="1:11" ht="39.54999999999999715783">
       <x:c r="A6" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E6" s="10" t="s">
-        <x:v>34</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F6" s="11" t="s">
         <x:v>42</x:v>
@@ -958,10 +973,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="H6" s="4" t="s">
-        <x:v>59</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="I6" s="5" t="s">
-        <x:v>45</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="J6" s="6">
         <x:v>37.349803420991499</x:v>
@@ -972,16 +987,16 @@
     </x:row>
     <x:row r="7" spans="1:11" ht="26.35000000000000142109">
       <x:c r="A7" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E7" s="9">
         <x:v>2</x:v>
@@ -993,7 +1008,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="H7" s="4" t="s">
-        <x:v>59</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="I7" s="5"/>
       <x:c r="J7" s="6">
@@ -1008,25 +1023,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E8" s="9">
         <x:v>2</x:v>
       </x:c>
       <x:c r="F8" s="3">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G8" s="3">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H8" s="4" t="s">
-        <x:v>61</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="I8" s="5"/>
       <x:c r="J8" s="6">
@@ -1038,16 +1053,16 @@
     </x:row>
     <x:row r="9" spans="1:11" ht="26.35000000000000142109">
       <x:c r="A9" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E9" s="9">
         <x:v>3</x:v>
@@ -1059,7 +1074,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="H9" s="4" t="s">
-        <x:v>61</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="I9" s="5"/>
       <x:c r="J9" s="6">
@@ -1071,16 +1086,16 @@
     </x:row>
     <x:row r="10" spans="1:11" ht="26.35000000000000142109">
       <x:c r="A10" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>0</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E10" s="9">
         <x:v>1</x:v>
@@ -1092,7 +1107,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="H10" s="4" t="s">
-        <x:v>59</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="I10" s="5"/>
       <x:c r="J10" s="6">
@@ -1104,16 +1119,16 @@
     </x:row>
     <x:row r="11" spans="1:11" ht="26.35000000000000142109">
       <x:c r="A11" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E11" s="9">
         <x:v>2</x:v>
@@ -1125,7 +1140,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="H11" s="4" t="s">
-        <x:v>61</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="I11" s="5"/>
       <x:c r="J11" s="6">
@@ -1137,16 +1152,16 @@
     </x:row>
     <x:row r="12" spans="1:11" ht="26.35000000000000142109">
       <x:c r="A12" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E12" s="9">
         <x:v>2</x:v>
@@ -1158,7 +1173,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="H12" s="4" t="s">
-        <x:v>61</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="I12" s="5"/>
       <x:c r="J12" s="6">
@@ -1170,16 +1185,16 @@
     </x:row>
     <x:row r="13" spans="1:11" ht="26.35000000000000142109">
       <x:c r="A13" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E13" s="9">
         <x:v>1</x:v>
@@ -1191,7 +1206,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H13" s="4" t="s">
-        <x:v>59</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="I13" s="5"/>
       <x:c r="J13" s="6">
@@ -1203,16 +1218,16 @@
     </x:row>
     <x:row r="14" spans="1:11" ht="26.35000000000000142109">
       <x:c r="A14" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E14" s="9">
         <x:v>3</x:v>
@@ -1224,7 +1239,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H14" s="4" t="s">
-        <x:v>61</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="I14" s="5"/>
       <x:c r="J14" s="6">
@@ -1236,16 +1251,16 @@
     </x:row>
     <x:row r="15" spans="1:11" ht="26.35000000000000142109">
       <x:c r="A15" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E15" s="9">
         <x:v>3</x:v>
@@ -1257,7 +1272,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="H15" s="4" t="s">
-        <x:v>59</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="I15" s="5"/>
       <x:c r="J15" s="6">
@@ -1269,16 +1284,16 @@
     </x:row>
     <x:row r="16" spans="1:11" ht="26.35000000000000142109">
       <x:c r="A16" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E16" s="9">
         <x:v>2</x:v>
@@ -1290,7 +1305,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="H16" s="4" t="s">
-        <x:v>59</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="I16" s="5"/>
       <x:c r="J16" s="6">
@@ -1302,13 +1317,13 @@
     </x:row>
     <x:row r="17" spans="1:11" ht="26.35000000000000142109">
       <x:c r="A17" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
         <x:v>19</x:v>
@@ -1323,7 +1338,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="H17" s="4" t="s">
-        <x:v>59</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="I17" s="5"/>
       <x:c r="J17" s="6">
@@ -1335,16 +1350,16 @@
     </x:row>
     <x:row r="18" spans="1:11" ht="26.35000000000000142109">
       <x:c r="A18" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E18" s="7">
         <x:v>0</x:v>
@@ -1356,7 +1371,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H18" s="4" t="s">
-        <x:v>59</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="I18" s="5"/>
       <x:c r="J18" s="6">
@@ -1368,16 +1383,16 @@
     </x:row>
     <x:row r="19" spans="1:11" ht="26.35000000000000142109">
       <x:c r="A19" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E19" s="9">
         <x:v>2</x:v>
@@ -1389,7 +1404,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H19" s="4" t="s">
-        <x:v>61</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="I19" s="5"/>
       <x:c r="J19" s="6">
